--- a/rules/CORE-000916/negative/01/data/unit-test-coreid-CG0370-negative.xlsx
+++ b/rules/CORE-000916/negative/01/data/unit-test-coreid-CG0370-negative.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000916\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2320E5-939D-4519-8E2E-9686444801AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C49B98C6-D26D-4966-B1E0-364C145F1C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32175" yWindow="675" windowWidth="21600" windowHeight="14505" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="195">
   <si>
     <t>Product</t>
   </si>
@@ -683,7 +683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -696,9 +696,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1079,7 +1076,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1124,7 +1121,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -1133,13 +1130,53 @@
         <v>194</v>
       </c>
       <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4">
         <v>6</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>194</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1290,7 +1327,7 @@
       <c r="C5" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -1415,7 +1452,7 @@
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -1438,7 +1475,7 @@
       <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>56</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1647,7 +1684,7 @@
       <c r="E5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G5" s="4" t="s">
